--- a/Perf/speedup/06fp_time.xlsx
+++ b/Perf/speedup/06fp_time.xlsx
@@ -5,15 +5,16 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\UTexas\26S\Perf\project\Perf\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\UTexas\26S\Perf\project\Perf\speedup\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D20C645D-38AA-4D13-9E85-960BE5373FF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B0AF284-D838-451C-9B98-70A667AB1CDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="ref" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="20">
   <si>
     <t>vm-small</t>
   </si>
@@ -82,6 +83,22 @@
   <si>
     <t>482</t>
   </si>
+  <si>
+    <t>Perf</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Perf error %</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Pin </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pin error %</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -110,12 +127,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -145,11 +168,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -165,6 +189,2176 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" altLang="zh-TW"/>
+              <a:t>2006</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" altLang="zh-TW" baseline="0"/>
+              <a:t> FP</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US" altLang="zh-TW"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US" altLang="zh-TW"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$N$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Perf error %</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:numRef>
+              <c:f>Sheet1!$L$4:$L$13</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>11</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$N$4:$N$13</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>14.222749880076764</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>21.334121978130955</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>21.445563487576447</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>23.438512021910302</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>23.77820075372491</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>24.319260121997335</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7.7318812822226226</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>11.264289659992254</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>14.069752762948077</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>16.610241715522665</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-4F3E-4EA9-A4E7-077640CFAD2D}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$P$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Pin error %</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:numRef>
+              <c:f>Sheet1!$L$4:$L$13</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>11</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$P$4:$P$13</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>15.580521185420203</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>39.501134310114061</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>20.115986934409044</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>8.3163434934623091</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2.2906233653955654</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>3.7429429241236685</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>18.631292522599658</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>21.383992889819865</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>23.43370869370127</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>24.294622503944595</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-4F3E-4EA9-A4E7-077640CFAD2D}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="689722928"/>
+        <c:axId val="689715248"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="689722928"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-TW"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="689715248"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="689715248"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-TW"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="689722928"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="zh-TW"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="zh-TW"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" altLang="zh-TW"/>
+              <a:t>2006</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" altLang="zh-TW" baseline="0"/>
+              <a:t> FP</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US" altLang="zh-TW"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US" altLang="zh-TW"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$N$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Perf error %</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:numRef>
+              <c:f>Sheet1!$L$4:$L$13</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>11</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$N$4:$N$13</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>14.222749880076764</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>21.334121978130955</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>21.445563487576447</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>23.438512021910302</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>23.77820075372491</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>24.319260121997335</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7.7318812822226226</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>11.264289659992254</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>14.069752762948077</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>16.610241715522665</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-2044-4DAB-9475-870B88C218C2}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$P$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Pin error %</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:numRef>
+              <c:f>Sheet1!$L$4:$L$13</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>11</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$P$4:$P$13</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>15.580521185420203</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>39.501134310114061</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>20.115986934409044</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>8.3163434934623091</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2.2906233653955654</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>3.7429429241236685</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>18.631292522599658</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>21.383992889819865</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>23.43370869370127</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>24.294622503944595</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-2044-4DAB-9475-870B88C218C2}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="689722928"/>
+        <c:axId val="689715248"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="689722928"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-TW"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="689715248"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="689715248"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-TW"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="689722928"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="zh-TW"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="zh-TW"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>590550</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>24493</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4DD914F8-2BD0-95E8-5330-5F89E1B40173}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>590550</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>24493</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{78851E66-85B1-407F-ADBA-15A9AC590B1A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -452,10 +2646,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I15"/>
-  <sheetFormatPr defaultRowHeight="15.45" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:P28"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -469,7 +2663,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -502,7 +2696,7 @@
         <v>0.93503120744528267</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
@@ -534,8 +2728,20 @@
         <f t="shared" ref="I3:I13" si="3">AVERAGE(F3:H3)</f>
         <v>1.0017195745341787</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="M3" t="s">
+        <v>16</v>
+      </c>
+      <c r="N3" t="s">
+        <v>17</v>
+      </c>
+      <c r="O3" t="s">
+        <v>18</v>
+      </c>
+      <c r="P3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
@@ -567,8 +2773,27 @@
         <f t="shared" si="3"/>
         <v>0.99045361862641856</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="L4">
+        <v>2</v>
+      </c>
+      <c r="M4">
+        <f>AVERAGE(AVERAGE(I3,I6),AVERAGE(I2,I4,I5,I7,I8,I9,I10,I11,I12,I13))</f>
+        <v>1.3073799621103184</v>
+      </c>
+      <c r="N4">
+        <f>100*ABS(M4-1.524157)/1.524157</f>
+        <v>14.222749880076764</v>
+      </c>
+      <c r="O4">
+        <f>AVERAGE(I3,AVERAGE(I2,I4,I5,I6,I7,I8,I9,I10,I11,I12,I13))</f>
+        <v>1.286685395715935</v>
+      </c>
+      <c r="P4">
+        <f>100*ABS(O4-1.524157)/1.524157</f>
+        <v>15.580521185420203</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>7</v>
       </c>
@@ -600,8 +2825,27 @@
         <f t="shared" si="3"/>
         <v>0.94542215891514336</v>
       </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="L5">
+        <v>3</v>
+      </c>
+      <c r="M5">
+        <f>AVERAGE(I3,I6,AVERAGE(I2,I4,I5,I7,I8,I9,I10,I11,I12,I13))</f>
+        <v>1.1989914864817786</v>
+      </c>
+      <c r="N5">
+        <f t="shared" ref="N5:N13" si="4">100*ABS(M5-1.524157)/1.524157</f>
+        <v>21.334121978130955</v>
+      </c>
+      <c r="O5">
+        <f>AVERAGE(I3,AVERAGE(I2,I4,I5,I7,I9,I10,I11,I12,I13),AVERAGE(I6,I8))</f>
+        <v>2.1262163036670052</v>
+      </c>
+      <c r="P5">
+        <f t="shared" ref="P5:P13" si="5">100*ABS(O5-1.524157)/1.524157</f>
+        <v>39.501134310114061</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>8</v>
       </c>
@@ -609,7 +2853,7 @@
         <v>7.1832890090000001</v>
       </c>
       <c r="C6">
-        <v>7.8806485999999995E-2</v>
+        <v>6.04</v>
       </c>
       <c r="D6">
         <v>7.364326202</v>
@@ -617,9 +2861,9 @@
       <c r="E6">
         <v>9.9295528859999997</v>
       </c>
-      <c r="F6">
+      <c r="F6" s="2">
         <f t="shared" si="0"/>
-        <v>91.150987356548299</v>
+        <v>1.1892862597682119</v>
       </c>
       <c r="G6">
         <f t="shared" si="1"/>
@@ -631,10 +2875,29 @@
       </c>
       <c r="I6">
         <f t="shared" si="3"/>
-        <v>30.949943194841911</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.4">
+        <v>0.96270949591521882</v>
+      </c>
+      <c r="L6">
+        <v>4</v>
+      </c>
+      <c r="M6">
+        <f>AVERAGE(I3,I6,AVERAGE(I4,I5,I7,I8,I9,I10,I11,I12),AVERAGE(I2,I13))</f>
+        <v>1.1972929429146595</v>
+      </c>
+      <c r="N6">
+        <f t="shared" si="4"/>
+        <v>21.445563487576447</v>
+      </c>
+      <c r="O6">
+        <f>AVERAGE(I3,AVERAGE(I2,I5,I9,I11,I12),AVERAGE(I4,I7,I10,I13),AVERAGE(I6,I8))</f>
+        <v>1.8307562229798808</v>
+      </c>
+      <c r="P6">
+        <f t="shared" si="5"/>
+        <v>20.115986934409044</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>9</v>
       </c>
@@ -666,8 +2929,27 @@
         <f t="shared" si="3"/>
         <v>0.77710725362761579</v>
       </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="L7">
+        <v>5</v>
+      </c>
+      <c r="M7">
+        <f>AVERAGE(I3,I6,AVERAGE(I4,I5,I7,I8,I9,I10,I11,I12),I2,I13)</f>
+        <v>1.1669172783222126</v>
+      </c>
+      <c r="N7">
+        <f t="shared" si="4"/>
+        <v>23.438512021910302</v>
+      </c>
+      <c r="O7">
+        <f>AVERAGE(I3,I5,AVERAGE(I2,I9,I11,I12),AVERAGE(I4,I7,I10,I13),AVERAGE(I6,I8))</f>
+        <v>1.6509111314996503</v>
+      </c>
+      <c r="P7">
+        <f t="shared" si="5"/>
+        <v>8.3163434934623091</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>10</v>
       </c>
@@ -699,8 +2981,27 @@
         <f t="shared" si="3"/>
         <v>7.92420497332105</v>
       </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="L8">
+        <v>6</v>
+      </c>
+      <c r="M8">
+        <f>AVERAGE(I3,I6,AVERAGE(I4,I5,I7,I8,I9,I11,I12),I10,I2,I13)</f>
+        <v>1.161739888738049</v>
+      </c>
+      <c r="N8">
+        <f t="shared" si="4"/>
+        <v>23.77820075372491</v>
+      </c>
+      <c r="O8">
+        <f>AVERAGE(I3,I5,AVERAGE(I2,I9,I11,I12),AVERAGE(I4,I7,I10),I13,AVERAGE(I6,I8))</f>
+        <v>1.5590696963673121</v>
+      </c>
+      <c r="P8">
+        <f t="shared" si="5"/>
+        <v>2.2906233653955654</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>11</v>
       </c>
@@ -732,8 +3033,27 @@
         <f t="shared" si="3"/>
         <v>0.94750168730659767</v>
       </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="L9">
+        <v>7</v>
+      </c>
+      <c r="M9">
+        <f>AVERAGE(I3,I6,AVERAGE(I4,I5,I7,I8,I11,I12),I9,I10,I2,I13)</f>
+        <v>1.153493294502369</v>
+      </c>
+      <c r="N9">
+        <f t="shared" si="4"/>
+        <v>24.319260121997335</v>
+      </c>
+      <c r="O9">
+        <f>AVERAGE(I3,I5,I2,AVERAGE(I9,I11,I12),AVERAGE(I4,I7,I10),I13,AVERAGE(I6,I8))</f>
+        <v>1.4671086734159644</v>
+      </c>
+      <c r="P9">
+        <f t="shared" si="5"/>
+        <v>3.7429429241236685</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>12</v>
       </c>
@@ -765,8 +3085,27 @@
         <f t="shared" si="3"/>
         <v>1.0286070840773007</v>
       </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="L10">
+        <v>8</v>
+      </c>
+      <c r="M10">
+        <f>AVERAGE(I3,I6,AVERAGE(I4,I5,I7,I11),AVERAGE(I8,I12),I9,I10,I2,I13)</f>
+        <v>1.4063109902053141</v>
+      </c>
+      <c r="N10">
+        <f t="shared" si="4"/>
+        <v>7.7318812822226226</v>
+      </c>
+      <c r="O10">
+        <f>AVERAGE(I3,I5,I2,,I11,AVERAGE(I9,I12),AVERAGE(I4,I7,I10),I13,AVERAGE(I6,I8))</f>
+        <v>1.2401868508263207</v>
+      </c>
+      <c r="P10">
+        <f t="shared" si="5"/>
+        <v>18.631292522599658</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>13</v>
       </c>
@@ -798,8 +3137,27 @@
         <f t="shared" si="3"/>
         <v>0.92756536655460764</v>
       </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="L11">
+        <v>9</v>
+      </c>
+      <c r="M11">
+        <f>AVERAGE(I3,I6,AVERAGE(I4,I5,I7),I11,AVERAGE(I8,I12),I9,I10,I2,I13)</f>
+        <v>1.3524715406469519</v>
+      </c>
+      <c r="N11">
+        <f t="shared" si="4"/>
+        <v>11.264289659992254</v>
+      </c>
+      <c r="O11">
+        <f>AVERAGE(I3,I5,I2,,I11,I9,I12,AVERAGE(I4,I7,I10),I13,AVERAGE(I6,I8))</f>
+        <v>1.1982313754903082</v>
+      </c>
+      <c r="P11">
+        <f t="shared" si="5"/>
+        <v>21.383992889819865</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>14</v>
       </c>
@@ -831,8 +3189,27 @@
         <f t="shared" si="3"/>
         <v>0.6937625076257935</v>
       </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="L12">
+        <v>10</v>
+      </c>
+      <c r="M12">
+        <f>AVERAGE(I3,I6,AVERAGE(I4,I7),I5,I11,AVERAGE(I8,I12),I9,I10,I2,I13)</f>
+        <v>1.3097118783808335</v>
+      </c>
+      <c r="N12">
+        <f t="shared" si="4"/>
+        <v>14.069752762948077</v>
+      </c>
+      <c r="O12">
+        <f>AVERAGE(I3,I5,I2,,I11,I9,I12,I7,AVERAGE(I4,I10),I13,AVERAGE(I6,I8))</f>
+        <v>1.1669904885853435</v>
+      </c>
+      <c r="P12">
+        <f t="shared" si="5"/>
+        <v>23.43370869370127</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>15</v>
       </c>
@@ -864,15 +3241,731 @@
         <f t="shared" si="3"/>
         <v>1.1557980324595667</v>
       </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="L13">
+        <v>11</v>
+      </c>
+      <c r="M13">
+        <f>AVERAGE(I3,I6,I4,I7,I5,I11,AVERAGE(I8,I12),I9,I10,I2,I13)</f>
+        <v>1.2709908381759412</v>
+      </c>
+      <c r="N13">
+        <f t="shared" si="4"/>
+        <v>16.610241715522665</v>
+      </c>
+      <c r="O13">
+        <f>AVERAGE(I3,I5,I2,,I11,I9,I12,I7,I4,I10,I13,AVERAGE(I6,I8))</f>
+        <v>1.1538688104825532</v>
+      </c>
+      <c r="P13">
+        <f t="shared" si="5"/>
+        <v>24.294622503944595</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="I15">
         <f>AVERAGE(I2:I13)</f>
-        <v>4.0230930549446224</v>
-      </c>
+        <v>1.5241569133673982</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" s="1"/>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" s="1"/>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" s="1"/>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" s="1"/>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" s="1"/>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" s="1"/>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23" s="1"/>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A24" s="1"/>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A25" s="1"/>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A26" s="1"/>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A27" s="1"/>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A28" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48B214B8-B4A8-48E7-A071-6013492BD9A2}">
+  <dimension ref="A1:P28"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2">
+        <v>172</v>
+      </c>
+      <c r="C2">
+        <v>145</v>
+      </c>
+      <c r="D2">
+        <v>2.0076473209999999</v>
+      </c>
+      <c r="E2">
+        <v>3.7326883209999999</v>
+      </c>
+      <c r="F2">
+        <f>B2/C2</f>
+        <v>1.1862068965517241</v>
+      </c>
+      <c r="G2">
+        <f>B2/D2</f>
+        <v>85.672417760270562</v>
+      </c>
+      <c r="H2">
+        <f>B2/E2</f>
+        <v>46.079389761082602</v>
+      </c>
+      <c r="I2">
+        <f>AVERAGE(F2:H2)</f>
+        <v>44.312671472634968</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3">
+        <v>177</v>
+      </c>
+      <c r="C3">
+        <v>145</v>
+      </c>
+      <c r="D3">
+        <v>4.9351610749999999</v>
+      </c>
+      <c r="E3">
+        <v>7.5743272939999997</v>
+      </c>
+      <c r="F3">
+        <f t="shared" ref="F3:F13" si="0">B3/C3</f>
+        <v>1.2206896551724138</v>
+      </c>
+      <c r="G3">
+        <f t="shared" ref="G3:G13" si="1">B3/D3</f>
+        <v>35.865090786322511</v>
+      </c>
+      <c r="H3">
+        <f t="shared" ref="H3:H13" si="2">B3/E3</f>
+        <v>23.368411890546437</v>
+      </c>
+      <c r="I3">
+        <f t="shared" ref="I3:I13" si="3">AVERAGE(F3:H3)</f>
+        <v>20.151397444013785</v>
+      </c>
+      <c r="M3" t="s">
+        <v>16</v>
+      </c>
+      <c r="N3" t="s">
+        <v>17</v>
+      </c>
+      <c r="O3" t="s">
+        <v>18</v>
+      </c>
+      <c r="P3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4">
+        <v>264</v>
+      </c>
+      <c r="C4">
+        <v>210</v>
+      </c>
+      <c r="D4">
+        <v>0.58973504200000004</v>
+      </c>
+      <c r="E4">
+        <v>0.68242471199999999</v>
+      </c>
+      <c r="F4">
+        <f t="shared" si="0"/>
+        <v>1.2571428571428571</v>
+      </c>
+      <c r="G4">
+        <f t="shared" si="1"/>
+        <v>447.65866227769448</v>
+      </c>
+      <c r="H4">
+        <f t="shared" si="2"/>
+        <v>386.855861691011</v>
+      </c>
+      <c r="I4">
+        <f t="shared" si="3"/>
+        <v>278.59055560861611</v>
+      </c>
+      <c r="L4">
+        <v>2</v>
+      </c>
+      <c r="M4" t="e">
+        <f>AVERAGE(AVERAGE(I3,I6),AVERAGE(I2,I4,I5,I7,I8,I9,I10,I11,I12,I13))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N4" t="e">
+        <f>100*ABS(M4-1.524157)/1.524157</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O4" t="e">
+        <f>AVERAGE(I3,AVERAGE(I2,I4,I5,I6,I7,I8,I9,I10,I11,I12,I13))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="P4" t="e">
+        <f>100*ABS(O4-1.524157)/1.524157</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5">
+        <v>275</v>
+      </c>
+      <c r="C5">
+        <v>233</v>
+      </c>
+      <c r="D5">
+        <v>0.82531859200000002</v>
+      </c>
+      <c r="E5">
+        <v>1.215476971</v>
+      </c>
+      <c r="F5">
+        <f t="shared" si="0"/>
+        <v>1.1802575107296138</v>
+      </c>
+      <c r="G5">
+        <f t="shared" si="1"/>
+        <v>333.20465898337596</v>
+      </c>
+      <c r="H5">
+        <f t="shared" si="2"/>
+        <v>226.24863042345538</v>
+      </c>
+      <c r="I5">
+        <f t="shared" si="3"/>
+        <v>186.87784897252035</v>
+      </c>
+      <c r="L5">
+        <v>3</v>
+      </c>
+      <c r="M5" t="e">
+        <f>AVERAGE(I3,I6,AVERAGE(I2,I4,I5,I7,I8,I9,I10,I11,I12,I13))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N5" t="e">
+        <f t="shared" ref="N5:N13" si="4">100*ABS(M5-1.524157)/1.524157</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O5" t="e">
+        <f>AVERAGE(I3,AVERAGE(I2,I4,I5,I7,I9,I10,I11,I12,I13),AVERAGE(I6,I8))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="P5" t="e">
+        <f t="shared" ref="P5:P13" si="5">100*ABS(O5-1.524157)/1.524157</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6">
+        <v>262</v>
+      </c>
+      <c r="C6">
+        <v>225</v>
+      </c>
+      <c r="D6">
+        <v>7.364326202</v>
+      </c>
+      <c r="E6">
+        <v>9.9295528859999997</v>
+      </c>
+      <c r="F6" s="2">
+        <f t="shared" si="0"/>
+        <v>1.1644444444444444</v>
+      </c>
+      <c r="G6">
+        <f t="shared" si="1"/>
+        <v>35.576914005906772</v>
+      </c>
+      <c r="H6">
+        <f t="shared" si="2"/>
+        <v>26.385880916088613</v>
+      </c>
+      <c r="I6">
+        <f t="shared" si="3"/>
+        <v>21.042413122146609</v>
+      </c>
+      <c r="L6">
+        <v>4</v>
+      </c>
+      <c r="M6" t="e">
+        <f>AVERAGE(I3,I6,AVERAGE(I4,I5,I7,I8,I9,I10,I11,I12),AVERAGE(I2,I13))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N6" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O6" t="e">
+        <f>AVERAGE(I3,AVERAGE(I2,I5,I9,I11,I12),AVERAGE(I4,I7,I10,I13),AVERAGE(I6,I8))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="P6" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7">
+        <v>99.2</v>
+      </c>
+      <c r="C7">
+        <v>84</v>
+      </c>
+      <c r="D7">
+        <v>0.316537978</v>
+      </c>
+      <c r="E7">
+        <v>0.40880669200000003</v>
+      </c>
+      <c r="F7">
+        <f t="shared" si="0"/>
+        <v>1.180952380952381</v>
+      </c>
+      <c r="G7">
+        <f t="shared" si="1"/>
+        <v>313.39051518172016</v>
+      </c>
+      <c r="H7">
+        <f t="shared" si="2"/>
+        <v>242.65747587126091</v>
+      </c>
+      <c r="I7">
+        <f t="shared" si="3"/>
+        <v>185.74298114464446</v>
+      </c>
+      <c r="L7">
+        <v>5</v>
+      </c>
+      <c r="M7" t="e">
+        <f>AVERAGE(I3,I6,AVERAGE(I4,I5,I7,I8,I9,I10,I11,I12),I2,I13)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N7" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O7" t="e">
+        <f>AVERAGE(I3,I5,AVERAGE(I2,I9,I11,I12),AVERAGE(I4,I7,I10,I13),AVERAGE(I6,I8))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="P7" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8">
+        <v>557</v>
+      </c>
+      <c r="C8">
+        <v>479</v>
+      </c>
+      <c r="D8">
+        <v>7.4319140000000004E-3</v>
+      </c>
+      <c r="E8">
+        <v>8.3658819999999998E-3</v>
+      </c>
+      <c r="F8">
+        <f t="shared" si="0"/>
+        <v>1.162839248434238</v>
+      </c>
+      <c r="G8">
+        <f t="shared" si="1"/>
+        <v>74947.045942673707</v>
+      </c>
+      <c r="H8">
+        <f t="shared" si="2"/>
+        <v>66579.94937055053</v>
+      </c>
+      <c r="I8">
+        <f t="shared" si="3"/>
+        <v>47176.052717490886</v>
+      </c>
+      <c r="L8">
+        <v>6</v>
+      </c>
+      <c r="M8" t="e">
+        <f>AVERAGE(I3,I6,AVERAGE(I4,I5,I7,I8,I9,I11,I12),I10,I2,I13)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N8" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O8" t="e">
+        <f>AVERAGE(I3,I5,AVERAGE(I2,I9,I11,I12),AVERAGE(I4,I7,I10),I13,AVERAGE(I6,I8))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="P8" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9">
+        <v>229</v>
+      </c>
+      <c r="C9">
+        <v>168</v>
+      </c>
+      <c r="D9">
+        <v>0.97321606500000002</v>
+      </c>
+      <c r="E9">
+        <v>1.269370479</v>
+      </c>
+      <c r="F9">
+        <f t="shared" si="0"/>
+        <v>1.3630952380952381</v>
+      </c>
+      <c r="G9">
+        <f t="shared" si="1"/>
+        <v>235.30232210048854</v>
+      </c>
+      <c r="H9">
+        <f t="shared" si="2"/>
+        <v>180.40438452641848</v>
+      </c>
+      <c r="I9">
+        <f t="shared" si="3"/>
+        <v>139.0232672883341</v>
+      </c>
+      <c r="L9">
+        <v>7</v>
+      </c>
+      <c r="M9" t="e">
+        <f>AVERAGE(I3,I6,AVERAGE(I4,I5,I7,I8,I11,I12),I9,I10,I2,I13)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N9" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O9" t="e">
+        <f>AVERAGE(I3,I5,I2,AVERAGE(I9,I11,I12),AVERAGE(I4,I7,I10),I13,AVERAGE(I6,I8))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="P9" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10">
+        <v>243</v>
+      </c>
+      <c r="C10">
+        <v>192</v>
+      </c>
+      <c r="D10">
+        <v>0.42635332799999998</v>
+      </c>
+      <c r="E10">
+        <v>0.55457910899999996</v>
+      </c>
+      <c r="F10">
+        <f t="shared" si="0"/>
+        <v>1.265625</v>
+      </c>
+      <c r="G10">
+        <f t="shared" si="1"/>
+        <v>569.94981401904295</v>
+      </c>
+      <c r="H10">
+        <f t="shared" si="2"/>
+        <v>438.17012948462872</v>
+      </c>
+      <c r="I10">
+        <f t="shared" si="3"/>
+        <v>336.46185616789057</v>
+      </c>
+      <c r="L10">
+        <v>8</v>
+      </c>
+      <c r="M10" t="e">
+        <f>AVERAGE(I3,I6,AVERAGE(I4,I5,I7,I11),AVERAGE(I8,I12),I9,I10,I2,I13)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N10" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O10" t="e">
+        <f>AVERAGE(I3,I5,I2,,I11,AVERAGE(I9,I12),AVERAGE(I4,I7,I10),I13,AVERAGE(I6,I8))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="P10" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11">
+        <v>187</v>
+      </c>
+      <c r="C11">
+        <v>159</v>
+      </c>
+      <c r="D11">
+        <v>1.431246115</v>
+      </c>
+      <c r="E11">
+        <v>1.993298338</v>
+      </c>
+      <c r="F11">
+        <f t="shared" si="0"/>
+        <v>1.1761006289308176</v>
+      </c>
+      <c r="G11">
+        <f t="shared" si="1"/>
+        <v>130.6553764863844</v>
+      </c>
+      <c r="H11">
+        <f t="shared" si="2"/>
+        <v>93.814356052505772</v>
+      </c>
+      <c r="I11">
+        <f t="shared" si="3"/>
+        <v>75.215277722606984</v>
+      </c>
+      <c r="L11">
+        <v>9</v>
+      </c>
+      <c r="M11" t="e">
+        <f>AVERAGE(I3,I6,AVERAGE(I4,I5,I7),I11,AVERAGE(I8,I12),I9,I10,I2,I13)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N11" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O11" t="e">
+        <f>AVERAGE(I3,I5,I2,,I11,I9,I12,AVERAGE(I4,I7,I10),I13,AVERAGE(I6,I8))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="P11" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D12">
+        <v>7.4246313999999994E-2</v>
+      </c>
+      <c r="E12">
+        <v>9.8946553000000007E-2</v>
+      </c>
+      <c r="F12" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G12">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I12" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="L12">
+        <v>10</v>
+      </c>
+      <c r="M12" t="e">
+        <f>AVERAGE(I3,I6,AVERAGE(I4,I7),I5,I11,AVERAGE(I8,I12),I9,I10,I2,I13)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N12" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O12" t="e">
+        <f>AVERAGE(I3,I5,I2,,I11,I9,I12,I7,AVERAGE(I4,I10),I13,AVERAGE(I6,I8))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="P12" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13">
+        <v>330</v>
+      </c>
+      <c r="C13">
+        <v>275</v>
+      </c>
+      <c r="D13">
+        <v>1.030329439</v>
+      </c>
+      <c r="E13">
+        <v>1.271350888</v>
+      </c>
+      <c r="F13">
+        <f t="shared" si="0"/>
+        <v>1.2</v>
+      </c>
+      <c r="G13">
+        <f t="shared" si="1"/>
+        <v>320.28590808808292</v>
+      </c>
+      <c r="H13">
+        <f t="shared" si="2"/>
+        <v>259.56642113109535</v>
+      </c>
+      <c r="I13">
+        <f t="shared" si="3"/>
+        <v>193.6841097397261</v>
+      </c>
+      <c r="L13">
+        <v>11</v>
+      </c>
+      <c r="M13" t="e">
+        <f>AVERAGE(I3,I6,I4,I7,I5,I11,AVERAGE(I8,I12),I9,I10,I2,I13)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N13" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O13" t="e">
+        <f>AVERAGE(I3,I5,I2,,I11,I9,I12,I7,I4,I10,I13,AVERAGE(I6,I8))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="P13" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="I15" t="e">
+        <f>AVERAGE(I2:I13)</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" s="1"/>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" s="1"/>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" s="1"/>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" s="1"/>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" s="1"/>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" s="1"/>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23" s="1"/>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A24" s="1"/>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A25" s="1"/>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A26" s="1"/>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A27" s="1"/>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A28" s="1"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/Perf/speedup/06fp_time.xlsx
+++ b/Perf/speedup/06fp_time.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\UTexas\26S\Perf\project\Perf\speedup\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B0AF284-D838-451C-9B98-70A667AB1CDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9EE6BE6-D196-4F77-9D81-36C505D9AF1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -732,7 +732,6 @@
               <a:rPr lang="en-US" altLang="zh-TW" baseline="0"/>
               <a:t> FP</a:t>
             </a:r>
-            <a:endParaRPr lang="en-US" altLang="zh-TW"/>
           </a:p>
         </c:rich>
       </c:tx>
@@ -761,7 +760,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="en-US" altLang="zh-TW"/>
+          <a:endParaRPr lang="zh-TW"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -777,7 +776,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$N$3</c:f>
+              <c:f>ref!$N$3</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -798,7 +797,7 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$L$4:$L$13</c:f>
+              <c:f>ref!$L$4:$L$13</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
@@ -837,46 +836,46 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$N$4:$N$13</c:f>
+              <c:f>ref!$N$4:$N$13</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>14.222749880076764</c:v>
+                  <c:v>118.84634319766323</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>21.334121978130955</c:v>
+                  <c:v>178.26835825977321</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>21.445563487576447</c:v>
+                  <c:v>116.10990225320242</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>23.438512021910302</c:v>
+                  <c:v>78.085111064070375</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>23.77820075372491</c:v>
+                  <c:v>53.109922244407109</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>24.319260121997335</c:v>
+                  <c:v>35.157440291336513</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>7.7318812822226226</c:v>
+                  <c:v>28.131126089265496</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>11.264289659992254</c:v>
+                  <c:v>16.44012915941466</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>14.069752762948077</c:v>
+                  <c:v>7.0950844711285797</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>16.610241715522665</c:v>
+                  <c:v>0.64372377271133641</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-2044-4DAB-9475-870B88C218C2}"/>
+              <c16:uniqueId val="{00000000-1A22-4C91-B3FF-09FDFE6BE5C2}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -885,7 +884,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$P$3</c:f>
+              <c:f>ref!$P$3</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -906,7 +905,7 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$L$4:$L$13</c:f>
+              <c:f>ref!$L$4:$L$13</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
@@ -945,46 +944,46 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$P$4:$P$13</c:f>
+              <c:f>ref!$P$4:$P$13</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>15.580521185420203</c:v>
+                  <c:v>34.135185857820638</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>39.501134310114061</c:v>
+                  <c:v>77.083981775328226</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>20.115986934409044</c:v>
+                  <c:v>38.681591731188618</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>8.3163434934623091</c:v>
+                  <c:v>15.576298816612475</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>2.2906233653955654</c:v>
+                  <c:v>0.87014262849952617</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>3.7429429241236685</c:v>
+                  <c:v>10.28948700907249</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>18.631292522599658</c:v>
+                  <c:v>27.761762899714874</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>21.383992889819865</c:v>
+                  <c:v>32.945735509901994</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>23.43370869370127</c:v>
+                  <c:v>37.110450762881321</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>24.294622503944595</c:v>
+                  <c:v>40.260082493881043</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-2044-4DAB-9475-870B88C218C2}"/>
+              <c16:uniqueId val="{00000001-1A22-4C91-B3FF-09FDFE6BE5C2}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -998,11 +997,11 @@
         </c:dLbls>
         <c:gapWidth val="219"/>
         <c:overlap val="-27"/>
-        <c:axId val="689722928"/>
-        <c:axId val="689715248"/>
+        <c:axId val="947365952"/>
+        <c:axId val="947367392"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="689722928"/>
+        <c:axId val="947365952"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1045,7 +1044,7 @@
             <a:endParaRPr lang="zh-TW"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="689715248"/>
+        <c:crossAx val="947367392"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1053,7 +1052,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="689715248"/>
+        <c:axId val="947367392"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1104,7 +1103,7 @@
             <a:endParaRPr lang="zh-TW"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="689722928"/>
+        <c:crossAx val="947365952"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2322,29 +2321,27 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>590550</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>348342</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>21771</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>18</xdr:col>
-      <xdr:colOff>24493</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
+      <xdr:colOff>391884</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>21771</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Chart 1">
+        <xdr:cNvPr id="3" name="Chart 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{78851E66-85B1-407F-ADBA-15A9AC590B1A}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7BDA8883-8976-B617-EBC3-24A74634C65A}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr>
-          <a:graphicFrameLocks/>
-        </xdr:cNvGraphicFramePr>
+        <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="0" y="0"/>
@@ -2647,9 +2644,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:P28"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.45" x14ac:dyDescent="0.4"/>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.4">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2663,7 +2660,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -2696,7 +2693,7 @@
         <v>0.93503120744528267</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
@@ -2741,7 +2738,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
@@ -2793,7 +2790,7 @@
         <v>15.580521185420203</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A5" s="1" t="s">
         <v>7</v>
       </c>
@@ -2845,7 +2842,7 @@
         <v>39.501134310114061</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A6" s="1" t="s">
         <v>8</v>
       </c>
@@ -2897,7 +2894,7 @@
         <v>20.115986934409044</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A7" s="1" t="s">
         <v>9</v>
       </c>
@@ -2949,7 +2946,7 @@
         <v>8.3163434934623091</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A8" s="1" t="s">
         <v>10</v>
       </c>
@@ -3001,7 +2998,7 @@
         <v>2.2906233653955654</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A9" s="1" t="s">
         <v>11</v>
       </c>
@@ -3053,7 +3050,7 @@
         <v>3.7429429241236685</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A10" s="1" t="s">
         <v>12</v>
       </c>
@@ -3105,7 +3102,7 @@
         <v>18.631292522599658</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A11" s="1" t="s">
         <v>13</v>
       </c>
@@ -3157,7 +3154,7 @@
         <v>21.383992889819865</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A12" s="1" t="s">
         <v>14</v>
       </c>
@@ -3209,7 +3206,7 @@
         <v>23.43370869370127</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A13" s="1" t="s">
         <v>15</v>
       </c>
@@ -3261,46 +3258,46 @@
         <v>24.294622503944595</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.4">
       <c r="I15">
         <f>AVERAGE(I2:I13)</f>
         <v>1.5241569133673982</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A17" s="1"/>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A18" s="1"/>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A19" s="1"/>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A20" s="1"/>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A21" s="1"/>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A22" s="1"/>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A23" s="1"/>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A24" s="1"/>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A25" s="1"/>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A26" s="1"/>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A27" s="1"/>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A28" s="1"/>
     </row>
   </sheetData>
@@ -3313,9 +3310,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48B214B8-B4A8-48E7-A071-6013492BD9A2}">
   <dimension ref="A1:P28"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.45" x14ac:dyDescent="0.4"/>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.4">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3329,15 +3326,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B2">
-        <v>172</v>
+        <v>2.249912401</v>
       </c>
       <c r="C2">
-        <v>145</v>
+        <v>2.0800488690000001</v>
       </c>
       <c r="D2">
         <v>2.0076473209999999</v>
@@ -3347,30 +3344,30 @@
       </c>
       <c r="F2">
         <f>B2/C2</f>
-        <v>1.1862068965517241</v>
+        <v>1.0816632409610949</v>
       </c>
       <c r="G2">
         <f>B2/D2</f>
-        <v>85.672417760270562</v>
+        <v>1.1206711345493336</v>
       </c>
       <c r="H2">
         <f>B2/E2</f>
-        <v>46.079389761082602</v>
+        <v>0.60275924682541959</v>
       </c>
       <c r="I2">
         <f>AVERAGE(F2:H2)</f>
-        <v>44.312671472634968</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+        <v>0.93503120744528267</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B3">
-        <v>177</v>
+        <v>5.2290646049999996</v>
       </c>
       <c r="C3">
-        <v>145</v>
+        <v>4.1657924140000002</v>
       </c>
       <c r="D3">
         <v>4.9351610749999999</v>
@@ -3380,19 +3377,19 @@
       </c>
       <c r="F3">
         <f t="shared" ref="F3:F13" si="0">B3/C3</f>
-        <v>1.2206896551724138</v>
+        <v>1.2552388802252015</v>
       </c>
       <c r="G3">
         <f t="shared" ref="G3:G13" si="1">B3/D3</f>
-        <v>35.865090786322511</v>
+        <v>1.0595529761913596</v>
       </c>
       <c r="H3">
         <f t="shared" ref="H3:H13" si="2">B3/E3</f>
-        <v>23.368411890546437</v>
+        <v>0.69036686718597451</v>
       </c>
       <c r="I3">
         <f t="shared" ref="I3:I13" si="3">AVERAGE(F3:H3)</f>
-        <v>20.151397444013785</v>
+        <v>1.0017195745341787</v>
       </c>
       <c r="M3" t="s">
         <v>16</v>
@@ -3407,15 +3404,15 @@
         <v>19</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B4">
-        <v>264</v>
+        <v>0.65718813899999995</v>
       </c>
       <c r="C4">
-        <v>210</v>
+        <v>0.73514024099999997</v>
       </c>
       <c r="D4">
         <v>0.58973504200000004</v>
@@ -3425,49 +3422,49 @@
       </c>
       <c r="F4">
         <f t="shared" si="0"/>
-        <v>1.2571428571428571</v>
+        <v>0.89396295066916354</v>
       </c>
       <c r="G4">
         <f t="shared" si="1"/>
-        <v>447.65866227769448</v>
+        <v>1.1143786483693467</v>
       </c>
       <c r="H4">
         <f t="shared" si="2"/>
-        <v>386.855861691011</v>
+        <v>0.96301925684074574</v>
       </c>
       <c r="I4">
         <f t="shared" si="3"/>
-        <v>278.59055560861611</v>
+        <v>0.99045361862641856</v>
       </c>
       <c r="L4">
         <v>2</v>
       </c>
-      <c r="M4" t="e">
+      <c r="M4">
         <f>AVERAGE(AVERAGE(I3,I6),AVERAGE(I2,I4,I5,I7,I8,I9,I10,I11,I12,I13))</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N4" t="e">
-        <f>100*ABS(M4-1.524157)/1.524157</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O4" t="e">
+        <v>8.8041883868419912</v>
+      </c>
+      <c r="N4">
+        <f>100*ABS(M4-4.023)/4.023</f>
+        <v>118.84634319766323</v>
+      </c>
+      <c r="O4">
         <f>AVERAGE(I3,AVERAGE(I2,I4,I5,I6,I7,I8,I9,I10,I11,I12,I13))</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P4" t="e">
-        <f>100*ABS(O4-1.524157)/1.524157</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+        <v>2.6497414729398754</v>
+      </c>
+      <c r="P4">
+        <f>100*ABS(O4-4.023)/4.023</f>
+        <v>34.135185857820638</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A5" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B5">
-        <v>275</v>
+        <v>0.88253232699999995</v>
       </c>
       <c r="C5">
-        <v>233</v>
+        <v>0.84788417900000002</v>
       </c>
       <c r="D5">
         <v>0.82531859200000002</v>
@@ -3477,49 +3474,49 @@
       </c>
       <c r="F5">
         <f t="shared" si="0"/>
-        <v>1.1802575107296138</v>
+        <v>1.0408642463890105</v>
       </c>
       <c r="G5">
         <f t="shared" si="1"/>
-        <v>333.20465898337596</v>
+        <v>1.0693232111266917</v>
       </c>
       <c r="H5">
         <f t="shared" si="2"/>
-        <v>226.24863042345538</v>
+        <v>0.72607901922972751</v>
       </c>
       <c r="I5">
         <f t="shared" si="3"/>
-        <v>186.87784897252035</v>
+        <v>0.94542215891514336</v>
       </c>
       <c r="L5">
         <v>3</v>
       </c>
-      <c r="M5" t="e">
+      <c r="M5">
         <f>AVERAGE(I3,I6,AVERAGE(I2,I4,I5,I7,I8,I9,I10,I11,I12,I13))</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N5" t="e">
-        <f t="shared" ref="N5:N13" si="4">100*ABS(M5-1.524157)/1.524157</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O5" t="e">
+        <v>11.194736052790676</v>
+      </c>
+      <c r="N5">
+        <f t="shared" ref="N5:N13" si="4">100*ABS(M5-4.023)/4.023</f>
+        <v>178.26835825977321</v>
+      </c>
+      <c r="O5">
         <f>AVERAGE(I3,AVERAGE(I2,I4,I5,I7,I9,I10,I11,I12,I13),AVERAGE(I6,I8))</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P5" t="e">
-        <f t="shared" ref="P5:P13" si="5">100*ABS(O5-1.524157)/1.524157</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+        <v>7.1240885868214541</v>
+      </c>
+      <c r="P5">
+        <f t="shared" ref="P5:P13" si="5">100*ABS(O5-4.023)/4.023</f>
+        <v>77.083981775328226</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A6" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B6">
-        <v>262</v>
+        <v>7.1832890090000001</v>
       </c>
       <c r="C6">
-        <v>225</v>
+        <v>7.8806485999999995E-2</v>
       </c>
       <c r="D6">
         <v>7.364326202</v>
@@ -3527,51 +3524,51 @@
       <c r="E6">
         <v>9.9295528859999997</v>
       </c>
-      <c r="F6" s="2">
+      <c r="F6">
         <f t="shared" si="0"/>
-        <v>1.1644444444444444</v>
+        <v>91.150987356548299</v>
       </c>
       <c r="G6">
         <f t="shared" si="1"/>
-        <v>35.576914005906772</v>
+        <v>0.97541700516323759</v>
       </c>
       <c r="H6">
         <f t="shared" si="2"/>
-        <v>26.385880916088613</v>
+        <v>0.72342522281420685</v>
       </c>
       <c r="I6">
         <f t="shared" si="3"/>
-        <v>21.042413122146609</v>
+        <v>30.949943194841911</v>
       </c>
       <c r="L6">
         <v>4</v>
       </c>
-      <c r="M6" t="e">
+      <c r="M6">
         <f>AVERAGE(I3,I6,AVERAGE(I4,I5,I7,I8,I9,I10,I11,I12),AVERAGE(I2,I13))</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N6" t="e">
+        <v>8.6941013676463328</v>
+      </c>
+      <c r="N6">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O6" t="e">
+        <v>116.10990225320242</v>
+      </c>
+      <c r="O6">
         <f>AVERAGE(I3,AVERAGE(I2,I5,I9,I11,I12),AVERAGE(I4,I7,I10,I13),AVERAGE(I6,I8))</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P6" t="e">
+        <v>5.5791604353457176</v>
+      </c>
+      <c r="P6">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+        <v>38.681591731188618</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A7" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B7">
-        <v>99.2</v>
+        <v>0.33585561800000002</v>
       </c>
       <c r="C7">
-        <v>84</v>
+        <v>0.74843693099999997</v>
       </c>
       <c r="D7">
         <v>0.316537978</v>
@@ -3581,49 +3578,49 @@
       </c>
       <c r="F7">
         <f t="shared" si="0"/>
-        <v>1.180952380952381</v>
+        <v>0.44874271176230884</v>
       </c>
       <c r="G7">
         <f t="shared" si="1"/>
-        <v>313.39051518172016</v>
+        <v>1.0610278745130546</v>
       </c>
       <c r="H7">
         <f t="shared" si="2"/>
-        <v>242.65747587126091</v>
+        <v>0.82155117460748417</v>
       </c>
       <c r="I7">
         <f t="shared" si="3"/>
-        <v>185.74298114464446</v>
+        <v>0.77710725362761579</v>
       </c>
       <c r="L7">
         <v>5</v>
       </c>
-      <c r="M7" t="e">
+      <c r="M7">
         <f>AVERAGE(I3,I6,AVERAGE(I4,I5,I7,I8,I9,I10,I11,I12),I2,I13)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N7" t="e">
+        <v>7.164364018107551</v>
+      </c>
+      <c r="N7">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O7" t="e">
+        <v>78.085111064070375</v>
+      </c>
+      <c r="O7">
         <f>AVERAGE(I3,I5,AVERAGE(I2,I9,I11,I12),AVERAGE(I4,I7,I10,I13),AVERAGE(I6,I8))</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P7" t="e">
+        <v>4.6496345013923195</v>
+      </c>
+      <c r="P7">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+        <v>15.576298816612475</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A8" s="1" t="s">
         <v>10</v>
       </c>
       <c r="B8">
-        <v>557</v>
+        <v>9.0052251E-2</v>
       </c>
       <c r="C8">
-        <v>479</v>
+        <v>0.10102090800000001</v>
       </c>
       <c r="D8">
         <v>7.4319140000000004E-3</v>
@@ -3633,49 +3630,49 @@
       </c>
       <c r="F8">
         <f t="shared" si="0"/>
-        <v>1.162839248434238</v>
+        <v>0.89142191238273161</v>
       </c>
       <c r="G8">
         <f t="shared" si="1"/>
-        <v>74947.045942673707</v>
+        <v>12.11696623507753</v>
       </c>
       <c r="H8">
         <f t="shared" si="2"/>
-        <v>66579.94937055053</v>
+        <v>10.764226772502887</v>
       </c>
       <c r="I8">
         <f t="shared" si="3"/>
-        <v>47176.052717490886</v>
+        <v>7.92420497332105</v>
       </c>
       <c r="L8">
         <v>6</v>
       </c>
-      <c r="M8" t="e">
+      <c r="M8">
         <f>AVERAGE(I3,I6,AVERAGE(I4,I5,I7,I8,I9,I11,I12),I10,I2,I13)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N8" t="e">
+        <v>6.1596121718924977</v>
+      </c>
+      <c r="N8">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O8" t="e">
+        <v>53.109922244407109</v>
+      </c>
+      <c r="O8">
         <f>AVERAGE(I3,I5,AVERAGE(I2,I9,I11,I12),AVERAGE(I4,I7,I10),I13,AVERAGE(I6,I8))</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P8" t="e">
+        <v>4.0580058379445356</v>
+      </c>
+      <c r="P8">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+        <v>0.87014262849952617</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A9" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B9">
-        <v>229</v>
+        <v>0.94558036400000001</v>
       </c>
       <c r="C9">
-        <v>168</v>
+        <v>0.83978387700000001</v>
       </c>
       <c r="D9">
         <v>0.97321606500000002</v>
@@ -3685,49 +3682,49 @@
       </c>
       <c r="F9">
         <f t="shared" si="0"/>
-        <v>1.3630952380952381</v>
+        <v>1.125980612271269</v>
       </c>
       <c r="G9">
         <f t="shared" si="1"/>
-        <v>235.30232210048854</v>
+        <v>0.9716037352918131</v>
       </c>
       <c r="H9">
         <f t="shared" si="2"/>
-        <v>180.40438452641848</v>
+        <v>0.7449207143567107</v>
       </c>
       <c r="I9">
         <f t="shared" si="3"/>
-        <v>139.0232672883341</v>
+        <v>0.94750168730659767</v>
       </c>
       <c r="L9">
         <v>7</v>
       </c>
-      <c r="M9" t="e">
+      <c r="M9">
         <f>AVERAGE(I3,I6,AVERAGE(I4,I5,I7,I8,I11,I12),I9,I10,I2,I13)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N9" t="e">
+        <v>5.4373838229204674</v>
+      </c>
+      <c r="N9">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O9" t="e">
+        <v>35.157440291336513</v>
+      </c>
+      <c r="O9">
         <f>AVERAGE(I3,I5,I2,AVERAGE(I9,I11,I12),AVERAGE(I4,I7,I10),I13,AVERAGE(I6,I8))</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P9" t="e">
+        <v>3.6090539376250135</v>
+      </c>
+      <c r="P9">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+        <v>10.28948700907249</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A10" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B10">
-        <v>243</v>
+        <v>0.521453897</v>
       </c>
       <c r="C10">
-        <v>192</v>
+        <v>0.56526422099999996</v>
       </c>
       <c r="D10">
         <v>0.42635332799999998</v>
@@ -3737,49 +3734,49 @@
       </c>
       <c r="F10">
         <f t="shared" si="0"/>
-        <v>1.265625</v>
+        <v>0.92249584818495001</v>
       </c>
       <c r="G10">
         <f t="shared" si="1"/>
-        <v>569.94981401904295</v>
+        <v>1.2230557679615439</v>
       </c>
       <c r="H10">
         <f t="shared" si="2"/>
-        <v>438.17012948462872</v>
+        <v>0.94026963608540837</v>
       </c>
       <c r="I10">
         <f t="shared" si="3"/>
-        <v>336.46185616789057</v>
+        <v>1.0286070840773007</v>
       </c>
       <c r="L10">
         <v>8</v>
       </c>
-      <c r="M10" t="e">
+      <c r="M10">
         <f>AVERAGE(I3,I6,AVERAGE(I4,I5,I7,I11),AVERAGE(I8,I12),I9,I10,I2,I13)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N10" t="e">
+        <v>5.1547152025711505</v>
+      </c>
+      <c r="N10">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O10" t="e">
+        <v>28.131126089265496</v>
+      </c>
+      <c r="O10">
         <f>AVERAGE(I3,I5,I2,,I11,AVERAGE(I9,I12),AVERAGE(I4,I7,I10),I13,AVERAGE(I6,I8))</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P10" t="e">
+        <v>2.9061442785444704</v>
+      </c>
+      <c r="P10">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+        <v>27.761762899714874</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A11" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B11">
-        <v>187</v>
+        <v>1.3637606120000001</v>
       </c>
       <c r="C11">
-        <v>159</v>
+        <v>1.1903557549999999</v>
       </c>
       <c r="D11">
         <v>1.431246115</v>
@@ -3789,95 +3786,101 @@
       </c>
       <c r="F11">
         <f t="shared" si="0"/>
-        <v>1.1761006289308176</v>
+        <v>1.1456748171894211</v>
       </c>
       <c r="G11">
         <f t="shared" si="1"/>
-        <v>130.6553764863844</v>
+        <v>0.95284842886717647</v>
       </c>
       <c r="H11">
         <f t="shared" si="2"/>
-        <v>93.814356052505772</v>
+        <v>0.68417285360722557</v>
       </c>
       <c r="I11">
         <f t="shared" si="3"/>
-        <v>75.215277722606984</v>
+        <v>0.92756536655460764</v>
       </c>
       <c r="L11">
         <v>9</v>
       </c>
-      <c r="M11" t="e">
+      <c r="M11">
         <f>AVERAGE(I3,I6,AVERAGE(I4,I5,I7),I11,AVERAGE(I8,I12),I9,I10,I2,I13)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N11" t="e">
+        <v>4.6843863960832515</v>
+      </c>
+      <c r="N11">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O11" t="e">
+        <v>16.44012915941466</v>
+      </c>
+      <c r="O11">
         <f>AVERAGE(I3,I5,I2,,I11,I9,I12,AVERAGE(I4,I7,I10),I13,AVERAGE(I6,I8))</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P11" t="e">
+        <v>2.6975930604366427</v>
+      </c>
+      <c r="P11">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+        <v>32.945735509901994</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A12" s="1" t="s">
         <v>14</v>
       </c>
+      <c r="B12">
+        <v>7.9424883000000002E-2</v>
+      </c>
+      <c r="C12">
+        <v>0.38032521699999999</v>
+      </c>
       <c r="D12">
         <v>7.4246313999999994E-2</v>
       </c>
       <c r="E12">
         <v>9.8946553000000007E-2</v>
       </c>
-      <c r="F12" t="e">
+      <c r="F12">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
+        <v>0.20883412261354209</v>
       </c>
       <c r="G12">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1.0697484995686117</v>
       </c>
       <c r="H12">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I12" t="e">
+        <v>0.80270490069522682</v>
+      </c>
+      <c r="I12">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
+        <v>0.6937625076257935</v>
       </c>
       <c r="L12">
         <v>10</v>
       </c>
-      <c r="M12" t="e">
+      <c r="M12">
         <f>AVERAGE(I3,I6,AVERAGE(I4,I7),I5,I11,AVERAGE(I8,I12),I9,I10,I2,I13)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N12" t="e">
+        <v>4.3084352482735024</v>
+      </c>
+      <c r="N12">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O12" t="e">
+        <v>7.0950844711285797</v>
+      </c>
+      <c r="O12">
         <f>AVERAGE(I3,I5,I2,,I11,I9,I12,I7,AVERAGE(I4,I10),I13,AVERAGE(I6,I8))</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P12" t="e">
+        <v>2.5300465658092843</v>
+      </c>
+      <c r="P12">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+        <v>37.110450762881321</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A13" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B13">
-        <v>330</v>
+        <v>1.437035431</v>
       </c>
       <c r="C13">
-        <v>275</v>
+        <v>1.524967309</v>
       </c>
       <c r="D13">
         <v>1.030329439</v>
@@ -3887,80 +3890,88 @@
       </c>
       <c r="F13">
         <f t="shared" si="0"/>
-        <v>1.2</v>
+        <v>0.94233851605798591</v>
       </c>
       <c r="G13">
         <f t="shared" si="1"/>
-        <v>320.28590808808292</v>
+        <v>1.3947339332502564</v>
       </c>
       <c r="H13">
         <f t="shared" si="2"/>
-        <v>259.56642113109535</v>
+        <v>1.1303216480704579</v>
       </c>
       <c r="I13">
         <f t="shared" si="3"/>
-        <v>193.6841097397261</v>
+        <v>1.1557980324595667</v>
       </c>
       <c r="L13">
         <v>11</v>
       </c>
-      <c r="M13" t="e">
+      <c r="M13">
         <f>AVERAGE(I3,I6,I4,I7,I5,I11,AVERAGE(I8,I12),I9,I10,I2,I13)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N13" t="e">
+        <v>3.9971029926238226</v>
+      </c>
+      <c r="N13">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O13" t="e">
+        <v>0.64372377271133641</v>
+      </c>
+      <c r="O13">
         <f>AVERAGE(I3,I5,I2,,I11,I9,I12,I7,I4,I10,I13,AVERAGE(I6,I8))</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P13" t="e">
+        <v>2.4033368812711653</v>
+      </c>
+      <c r="P13">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="I15" t="e">
+        <v>40.260082493881043</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="I15">
         <f>AVERAGE(I2:I13)</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+        <v>4.0230930549446224</v>
+      </c>
+      <c r="N15">
+        <f>AVERAGE(N4:N13)</f>
+        <v>63.188714080297316</v>
+      </c>
+      <c r="P15">
+        <f>AVERAGE(P4:P13)</f>
+        <v>31.471471948490127</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A17" s="1"/>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A18" s="1"/>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A19" s="1"/>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A20" s="1"/>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A21" s="1"/>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A22" s="1"/>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A23" s="1"/>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A24" s="1"/>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A25" s="1"/>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A26" s="1"/>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A27" s="1"/>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A28" s="1"/>
     </row>
   </sheetData>
